--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72870969</v>
+        <v>136864262</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>58283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>103019</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klotsboda, Vstm</t>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517129</v>
+        <v>517134</v>
       </c>
       <c r="R2" t="n">
-        <v>6636328</v>
+        <v>6636298</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,17 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Båda sidor av vägen. Rikligt antal.</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,29 +773,491 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136864262</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136864316</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98374</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>517115</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6636255</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136864316</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136864335</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106369</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>517115</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6636255</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136864335</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136864321</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98404</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517115</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6636255</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136864321</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>72870969</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Klotsboda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>517129</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6636328</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-07-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-07-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Båda sidor av vägen. Rikligt antal.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/72870969</t>
         </is>
@@ -793,6 +1266,10 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136864262</v>
+        <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>58283</v>
+        <v>96568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103019</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärtmes</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aegithalos caudatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517134</v>
+        <v>517080</v>
       </c>
       <c r="R2" t="n">
-        <v>6636298</v>
+        <v>6636468</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,8 +763,14 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -788,16 +786,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136864262</t>
+          <t>https://artportalen.se/Sighting/136868338</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136864316</v>
+        <v>136864262</v>
       </c>
       <c r="B3" t="n">
-        <v>98374</v>
+        <v>58283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,41 +803,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219815</v>
+        <v>103019</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517115</v>
+        <v>517134</v>
       </c>
       <c r="R3" t="n">
-        <v>6636255</v>
+        <v>6636298</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,19 +883,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Gräsblandskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -905,16 +900,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136864316</t>
+          <t>https://artportalen.se/Sighting/136864262</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136864335</v>
+        <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>106369</v>
+        <v>98374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,30 +917,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221154</v>
+        <v>219815</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1026,16 +1017,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136864335</t>
+          <t>https://artportalen.se/Sighting/136864316</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136864321</v>
+        <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98404</v>
+        <v>98374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,45 +1034,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223358</v>
+        <v>219815</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517115</v>
+        <v>517093</v>
       </c>
       <c r="R5" t="n">
-        <v>6636255</v>
+        <v>6636466</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,12 +1112,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Gräsblandskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1147,16 +1129,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136864321</t>
+          <t>https://artportalen.se/Sighting/136868331</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72870969</v>
+        <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>98374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,33 +1146,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>219815</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klotsboda, Vstm</t>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517129</v>
+        <v>517080</v>
       </c>
       <c r="R6" t="n">
-        <v>6636328</v>
+        <v>6636468</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,17 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Båda sidor av vägen. Rikligt antal.</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,31 +1218,1169 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868340</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136868333</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517093</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6636466</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868333</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136868346</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517080</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6636468</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868346</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136864335</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106369</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>517115</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6636255</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136864335</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136868334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>517093</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6636466</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868334</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136868327</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>517093</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6636466</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868327</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136868351</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>517080</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6636468</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868351</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136868170</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104073</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>517120</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6636244</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868170</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136868216</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104073</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>517130</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6636178</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Mad (strandkärr)</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868216</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136864321</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98404</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>517115</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6636255</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136864321</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>72870969</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klotsboda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>517129</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6636328</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-07-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-07-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Båda sidor av vägen. Rikligt antal.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/72870969</t>
         </is>
@@ -1270,6 +2393,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136864335</v>
+        <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>106369</v>
+        <v>111332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,28 +1490,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221154</v>
+        <v>220240</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517115</v>
+        <v>517130</v>
       </c>
       <c r="R9" t="n">
-        <v>6636255</v>
+        <v>6636206</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1570,16 +1570,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Gräsblandskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1591,19 +1581,23 @@
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136864335</t>
+          <t>https://artportalen.se/Sighting/137008717</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136868334</v>
+        <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>98215</v>
+        <v>106369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,41 +1605,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221154</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517093</v>
+        <v>517115</v>
       </c>
       <c r="R10" t="n">
-        <v>6636466</v>
+        <v>6636255</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,7 +1687,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1706,16 +1709,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136868334</t>
+          <t>https://artportalen.se/Sighting/136864335</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136868327</v>
+        <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98432</v>
+        <v>98215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222736</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Majbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Athyrium filix-femina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1818,13 +1821,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136868327</t>
+          <t>https://artportalen.se/Sighting/136868334</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136868351</v>
+        <v>136868327</v>
       </c>
       <c r="B12" t="n">
         <v>98432</v>
@@ -1863,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517080</v>
+        <v>517093</v>
       </c>
       <c r="R12" t="n">
-        <v>6636468</v>
+        <v>6636466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,16 +1933,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136868351</t>
+          <t>https://artportalen.se/Sighting/136868327</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136868170</v>
+        <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>104073</v>
+        <v>98432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223284</v>
+        <v>222736</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Majbräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Athyrium filix-femina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,14 +1974,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sjöbroviken Ö om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517120</v>
+        <v>517080</v>
       </c>
       <c r="R13" t="n">
-        <v>6636244</v>
+        <v>6636468</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,6 +2026,11 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -2037,13 +2045,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136868170</t>
+          <t>https://artportalen.se/Sighting/136868351</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136868216</v>
+        <v>136868170</v>
       </c>
       <c r="B14" t="n">
         <v>104073</v>
@@ -2082,13 +2090,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517130</v>
+        <v>517120</v>
       </c>
       <c r="R14" t="n">
-        <v>6636178</v>
+        <v>6636244</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,11 +2138,6 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Mad (strandkärr)</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
@@ -2149,16 +2152,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136868216</t>
+          <t>https://artportalen.se/Sighting/136868170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136864321</v>
+        <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>98404</v>
+        <v>104073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,30 +2169,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223358</v>
+        <v>223284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2198,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517115</v>
+        <v>517130</v>
       </c>
       <c r="R15" t="n">
-        <v>6636255</v>
+        <v>6636178</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,12 +2247,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Gräsblandskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
+          <t>Mad (strandkärr)</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2270,16 +2264,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136864321</t>
+          <t>https://artportalen.se/Sighting/136868216</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>72870969</v>
+        <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>99038</v>
+        <v>104073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,33 +2281,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223597</v>
+        <v>223284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Klotsboda, Vstm</t>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517129</v>
+        <v>517122</v>
       </c>
       <c r="R16" t="n">
-        <v>6636328</v>
+        <v>6636256</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2337,17 +2339,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Båda sidor av vägen. Rikligt antal.</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,26 +2358,264 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Olikåldrig, flerskiktad blandskog av gran, tall (äldre överståndare), glasbjörk, klibbal och rönn med piprör helt dominerande i fältskiktet.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137008662</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136864321</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98404</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sjöbroviken, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>517115</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6636255</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Blandskog av gran, tall, vårtbjörk, glasbjörk, sälg, rönn, klibbal med piprör som dominant i fältskiktet</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136864321</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>72870969</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klotsboda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>517129</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6636328</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-07-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-07-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Båda sidor av vägen. Rikligt antal.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/72870969</t>
         </is>
@@ -2403,6 +2638,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106369</v>
+        <v>106375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98432</v>
+        <v>98438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98432</v>
+        <v>98438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106375</v>
+        <v>106377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98438</v>
+        <v>98440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98438</v>
+        <v>98440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98382</v>
+        <v>98383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98382</v>
+        <v>98383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98382</v>
+        <v>98383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106377</v>
+        <v>106378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98440</v>
+        <v>98441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98440</v>
+        <v>98441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98412</v>
+        <v>98413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98383</v>
+        <v>98389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98383</v>
+        <v>98389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98383</v>
+        <v>98389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106378</v>
+        <v>106384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98441</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98441</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98413</v>
+        <v>98419</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98389</v>
+        <v>98393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98389</v>
+        <v>98393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98389</v>
+        <v>98393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106384</v>
+        <v>106388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98419</v>
+        <v>98423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98393</v>
+        <v>98395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98393</v>
+        <v>98395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98393</v>
+        <v>98395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106388</v>
+        <v>106390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98451</v>
+        <v>98453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98451</v>
+        <v>98453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98423</v>
+        <v>98425</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98395</v>
+        <v>98397</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98395</v>
+        <v>98397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98395</v>
+        <v>98397</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106390</v>
+        <v>106392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98425</v>
+        <v>98427</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136864262</v>
       </c>
       <c r="B3" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98397</v>
+        <v>98410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98397</v>
+        <v>98410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98397</v>
+        <v>98410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106392</v>
+        <v>106405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98455</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98455</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98427</v>
+        <v>98440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136864262</v>
       </c>
       <c r="B3" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106405</v>
+        <v>106407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98440</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -827,11 +827,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -1277,11 +1273,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1393,11 +1385,7 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1509,11 +1497,7 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1624,11 +1608,7 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -2420,11 +2400,7 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98412</v>
+        <v>98415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98412</v>
+        <v>98415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98412</v>
+        <v>98415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106407</v>
+        <v>106411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136864262</v>
       </c>
       <c r="B3" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98415</v>
+        <v>98425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98415</v>
+        <v>98425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98415</v>
+        <v>98425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106411</v>
+        <v>106430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98473</v>
+        <v>98483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98473</v>
+        <v>98483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98445</v>
+        <v>98455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106430</v>
+        <v>106431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136864262</v>
       </c>
       <c r="B3" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98426</v>
+        <v>98431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98426</v>
+        <v>98431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98426</v>
+        <v>98431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106431</v>
+        <v>106436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98484</v>
+        <v>98489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98484</v>
+        <v>98489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>98461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
+        <v>98433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
+        <v>98433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
+        <v>98433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106436</v>
+        <v>106439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98489</v>
+        <v>98491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98489</v>
+        <v>98491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98461</v>
+        <v>98463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136864262</v>
       </c>
       <c r="B3" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98433</v>
+        <v>98439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98433</v>
+        <v>98439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98433</v>
+        <v>98439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106439</v>
+        <v>106445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98491</v>
+        <v>98497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98491</v>
+        <v>98497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98463</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106445</v>
+        <v>106446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136864316</v>
       </c>
       <c r="B4" t="n">
-        <v>98439</v>
+        <v>98451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98439</v>
+        <v>98451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98439</v>
+        <v>98451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136864335</v>
       </c>
       <c r="B10" t="n">
-        <v>106446</v>
+        <v>106458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98497</v>
+        <v>98509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98497</v>
+        <v>98509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136864321</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868338</v>
       </c>
       <c r="B2" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>136868331</v>
       </c>
       <c r="B5" t="n">
-        <v>98451</v>
+        <v>98452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136868340</v>
       </c>
       <c r="B6" t="n">
-        <v>98451</v>
+        <v>98452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136868333</v>
       </c>
       <c r="B7" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136868346</v>
       </c>
       <c r="B8" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>136868334</v>
       </c>
       <c r="B11" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136868327</v>
       </c>
       <c r="B12" t="n">
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136868351</v>
       </c>
       <c r="B13" t="n">
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136868170</v>
       </c>
       <c r="B14" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136868216</v>
       </c>
       <c r="B15" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104158</v>
+        <v>104161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104161</v>
+        <v>104162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 2457-2026 artfynd.xlsx
+++ b/artfynd/S 2457-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137008717</v>
       </c>
       <c r="B9" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137008662</v>
       </c>
       <c r="B16" t="n">
-        <v>104162</v>
+        <v>104166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
